--- a/education_forms/043_madison_city_schools--education_forms.xlsx
+++ b/education_forms/043_madison_city_schools--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>$50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>$50</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>$50</t>
+          <t>000-$75</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>$50</t>
+          <t>000-$75</t>
         </is>
       </c>
     </row>
@@ -1709,70 +1709,70 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>000-$75</t>
+          <t>more_than_$75</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>000-$75</t>
+          <t>More than $75</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>parent_income_choices</t>
+          <t>student_physical_capability_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>parent_income_choices</t>
+          <t>student_physical_capability_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>more_than_$75</t>
+          <t>partially</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>More than $75</t>
+          <t>Partially</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>parent_income_choices</t>
+          <t>student_physical_capability_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>fully</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Fully</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>student_physical_capability_choices</t>
+          <t>student_english_proficiency_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>student_physical_capability_choices</t>
+          <t>student_english_proficiency_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>student_physical_capability_choices</t>
+          <t>student_english_proficiency_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>student_english_proficiency_choices</t>
+          <t>student_math_proficiency_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>student_english_proficiency_choices</t>
+          <t>student_math_proficiency_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>student_english_proficiency_choices</t>
+          <t>student_math_proficiency_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>student_math_proficiency_choices</t>
+          <t>student_science_proficiency_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>student_math_proficiency_choices</t>
+          <t>student_science_proficiency_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>student_math_proficiency_choices</t>
+          <t>student_science_proficiency_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>student_science_proficiency_choices</t>
+          <t>parent_english_proficiency_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>student_science_proficiency_choices</t>
+          <t>parent_english_proficiency_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>student_science_proficiency_choices</t>
+          <t>parent_english_proficiency_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>parent_english_proficiency_choices</t>
+          <t>parent_math_proficiency_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>parent_english_proficiency_choices</t>
+          <t>parent_math_proficiency_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>parent_english_proficiency_choices</t>
+          <t>parent_math_proficiency_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2027,7 +2027,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>parent_math_proficiency_choices</t>
+          <t>parent_science_proficiency_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>parent_math_proficiency_choices</t>
+          <t>parent_science_proficiency_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>parent_math_proficiency_choices</t>
+          <t>parent_science_proficiency_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2070,57 +2070,6 @@
         </is>
       </c>
       <c r="C57" t="inlineStr">
-        <is>
-          <t>Fully</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>parent_science_proficiency_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>parent_science_proficiency_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>partially</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Partially</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>parent_science_proficiency_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>fully</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
         <is>
           <t>Fully</t>
         </is>
